--- a/download/S库物料库存查询.xlsx
+++ b/download/S库物料库存查询.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="78">
   <si>
     <t>序号</t>
   </si>
@@ -112,19 +112,19 @@
     <t>库位调整时间</t>
   </si>
   <si>
-    <t>711W61900-7132/K</t>
-  </si>
-  <si>
-    <t>711W61900-7132</t>
-  </si>
-  <si>
-    <t>过滤器系统总成</t>
-  </si>
-  <si>
-    <t>101392</t>
-  </si>
-  <si>
-    <t>湖北美标汽车制冷系统有限公司</t>
+    <t>712W25441-0024/2</t>
+  </si>
+  <si>
+    <t>712W25441-0024</t>
+  </si>
+  <si>
+    <t>电瓶箱体固定支架（前/T7-S32大油箱）</t>
+  </si>
+  <si>
+    <t>N0381</t>
+  </si>
+  <si>
+    <t>重汽（济南）传动轴有限公司</t>
   </si>
   <si>
     <t>312302</t>
@@ -133,220 +133,115 @@
     <t>制造部平面仓储库</t>
   </si>
   <si>
-    <t>待检</t>
+    <t>合格</t>
   </si>
   <si>
     <t>EA</t>
   </si>
   <si>
-    <t>312302.S01</t>
-  </si>
-  <si>
-    <t>1004库来料暂存区</t>
-  </si>
-  <si>
-    <t>312302.S01.010101</t>
-  </si>
-  <si>
-    <t>平面库存储区</t>
+    <t>312302.S05</t>
+  </si>
+  <si>
+    <t>1102库来料暂存区</t>
+  </si>
+  <si>
+    <t>312302.S05.010101</t>
+  </si>
+  <si>
+    <t>物料储存库位</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>托管</t>
-  </si>
-  <si>
-    <t>20231106</t>
-  </si>
-  <si>
-    <t>PH202311080458</t>
-  </si>
-  <si>
-    <t>TP2023110882834</t>
-  </si>
-  <si>
-    <t>刘兵</t>
-  </si>
-  <si>
-    <t>711W62645-0011/1</t>
-  </si>
-  <si>
-    <t>711W62645-0011</t>
-  </si>
-  <si>
-    <t>车门玻璃托架</t>
-  </si>
-  <si>
-    <t>104391</t>
-  </si>
-  <si>
-    <t>泰安晟泰汽车零部件有限公司</t>
-  </si>
-  <si>
-    <t>23110801</t>
-  </si>
-  <si>
-    <t>PH202311080450</t>
-  </si>
-  <si>
-    <t>TP2023110882815</t>
-  </si>
-  <si>
-    <t>711W62645-0032/1</t>
-  </si>
-  <si>
-    <t>711W62645-0032</t>
-  </si>
-  <si>
-    <t>左隔水板</t>
-  </si>
-  <si>
-    <t>TP2023110882801</t>
-  </si>
-  <si>
-    <t>711W62645-0033/1</t>
-  </si>
-  <si>
-    <t>711W62645-0033</t>
-  </si>
-  <si>
-    <t>右隔水板(与左件对称)</t>
-  </si>
-  <si>
-    <t>TP2023110882802</t>
-  </si>
-  <si>
-    <t>711W62645-6050/1</t>
-  </si>
-  <si>
-    <t>711W62645-6050</t>
-  </si>
-  <si>
-    <t>右车门电动玻璃升降器</t>
-  </si>
-  <si>
-    <t>TP2023110882814</t>
-  </si>
-  <si>
-    <t>711W62645-6051/1</t>
-  </si>
-  <si>
-    <t>711W62645-6051</t>
-  </si>
-  <si>
-    <t>左车门电动玻璃升降器</t>
-  </si>
-  <si>
-    <t>TP2023110882803</t>
-  </si>
-  <si>
-    <t>711W62651-0057/1</t>
-  </si>
-  <si>
-    <t>711W62651-0057</t>
-  </si>
-  <si>
-    <t>左车门玻璃后导轨</t>
-  </si>
-  <si>
-    <t>TP2023110882799</t>
-  </si>
-  <si>
-    <t>711W62651-0058/1</t>
-  </si>
-  <si>
-    <t>711W62651-0058</t>
-  </si>
-  <si>
-    <t>右车门玻璃后导轨（与左件对称）</t>
-  </si>
-  <si>
-    <t>TP2023110882797</t>
-  </si>
-  <si>
-    <t>WG9925682121/1</t>
-  </si>
-  <si>
-    <t>WG9925682121</t>
-  </si>
-  <si>
-    <t>前稳定杆右支架</t>
-  </si>
-  <si>
-    <t>103452</t>
-  </si>
-  <si>
-    <t>山东宝泉实业有限公司</t>
-  </si>
-  <si>
-    <t>PH202311080518</t>
-  </si>
-  <si>
-    <t>TP2023110883417</t>
-  </si>
-  <si>
-    <t>YG1671821000/1</t>
-  </si>
-  <si>
-    <t>YG1671821000</t>
-  </si>
-  <si>
-    <t>空调HVAC总成(豪沃NX)</t>
-  </si>
-  <si>
-    <t>PH202311080462</t>
-  </si>
-  <si>
-    <t>TP2023110882841</t>
-  </si>
-  <si>
-    <t>YZ167182500008/1</t>
-  </si>
-  <si>
-    <t>YZ167182500008</t>
-  </si>
-  <si>
-    <t>独立暖风支架</t>
-  </si>
-  <si>
-    <t>PH202311080524</t>
-  </si>
-  <si>
-    <t>TP2023110883363</t>
-  </si>
-  <si>
-    <t>YZ952524000108/1</t>
-  </si>
-  <si>
-    <t>YZ952524000108</t>
-  </si>
-  <si>
-    <t>管夹支架</t>
-  </si>
-  <si>
-    <t>105538</t>
-  </si>
-  <si>
-    <t>邹城市永进机械有限公司</t>
-  </si>
-  <si>
-    <t>PH202311080478</t>
-  </si>
-  <si>
-    <t>TP2023110882920</t>
-  </si>
-  <si>
-    <t>PH202311080482</t>
-  </si>
-  <si>
-    <t>TP2023110882955</t>
+    <t>非托</t>
+  </si>
+  <si>
+    <t>23111601</t>
+  </si>
+  <si>
+    <t>PH202311161714</t>
+  </si>
+  <si>
+    <t>TP20231116231197</t>
+  </si>
+  <si>
+    <t>卢慧</t>
+  </si>
+  <si>
+    <t>PH202311161713</t>
+  </si>
+  <si>
+    <t>TP20231116231187</t>
+  </si>
+  <si>
+    <t>712W25441-0025/2</t>
+  </si>
+  <si>
+    <t>712W25441-0025</t>
+  </si>
+  <si>
+    <t>电瓶箱体固定支架（后/T7-S32大油箱）</t>
+  </si>
+  <si>
+    <t>TP20231116231196</t>
+  </si>
+  <si>
+    <t>TP20231116231186</t>
+  </si>
+  <si>
+    <t>712W25441-0045/2</t>
+  </si>
+  <si>
+    <t>712W25441-0045</t>
+  </si>
+  <si>
+    <t>电瓶箱后挡板</t>
+  </si>
+  <si>
+    <t>TP20231116231194</t>
+  </si>
+  <si>
+    <t>TP20231116231183</t>
+  </si>
+  <si>
+    <t>811W41860-0150/1</t>
+  </si>
+  <si>
+    <t>811W41860-0150</t>
+  </si>
+  <si>
+    <t>蓄电池压板</t>
+  </si>
+  <si>
+    <t>TP20231116231195</t>
+  </si>
+  <si>
+    <t>TP20231116231185</t>
+  </si>
+  <si>
+    <t>AZ1664440069</t>
+  </si>
+  <si>
+    <t>驾驶室后减振器总成（空气弹簧/395sus）</t>
+  </si>
+  <si>
+    <t>PH202311161717</t>
+  </si>
+  <si>
+    <t>TP20231116231203</t>
+  </si>
+  <si>
+    <t>PH202311161716</t>
+  </si>
+  <si>
+    <t>TP20231116231201</t>
   </si>
   <si>
     <t>合计:0</t>
   </si>
   <si>
-    <t>合计:4777</t>
+    <t>合计:106</t>
   </si>
   <si>
     <t>平均：0</t>
@@ -753,7 +648,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11.35" customWidth="1"/>
@@ -913,10 +808,10 @@
         <v>40</v>
       </c>
       <c r="K2" s="4">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="L2" s="4">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>41</v>
@@ -958,7 +853,7 @@
         <v>50</v>
       </c>
       <c r="Z2" s="5">
-        <v>45238.46053240741</v>
+        <v>45246.73003472222</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>46</v>
@@ -970,13 +865,13 @@
         <v>46</v>
       </c>
       <c r="AE2" s="5">
-        <v>45238.46071759259</v>
+        <v>45246.73850694444</v>
       </c>
       <c r="AF2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG2" s="5">
-        <v>45238.460740740746</v>
+        <v>45246.738530092596</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -984,19 +879,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>38</v>
@@ -1011,10 +906,10 @@
         <v>40</v>
       </c>
       <c r="K3" s="4">
-        <v>960</v>
+        <v>7</v>
       </c>
       <c r="L3" s="4">
-        <v>960</v>
+        <v>7</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>41</v>
@@ -1035,10 +930,10 @@
         <v>45</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>46</v>
@@ -1047,16 +942,16 @@
         <v>47</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Z3" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.72951388889</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>46</v>
@@ -1068,13 +963,13 @@
         <v>46</v>
       </c>
       <c r="AE3" s="5">
-        <v>45238.46041666667</v>
+        <v>45246.738645833335</v>
       </c>
       <c r="AF3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG3" s="5">
-        <v>45238.460439814815</v>
+        <v>45246.73866898148</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1082,19 +977,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>38</v>
@@ -1109,10 +1004,10 @@
         <v>40</v>
       </c>
       <c r="K4" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="L4" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>41</v>
@@ -1133,10 +1028,10 @@
         <v>45</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>46</v>
@@ -1145,31 +1040,34 @@
         <v>47</v>
       </c>
       <c r="W4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="X4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="Z4" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.73003472222</v>
       </c>
       <c r="AB4" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
       <c r="AD4" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE4" s="5">
-        <v>45238.46030092593</v>
+        <v>45246.738483796296</v>
       </c>
       <c r="AF4" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG4" s="5">
-        <v>45238.46032407407</v>
+        <v>45246.73850694444</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1177,19 +1075,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>38</v>
@@ -1204,10 +1102,10 @@
         <v>40</v>
       </c>
       <c r="K5" s="4">
-        <v>480</v>
+        <v>7</v>
       </c>
       <c r="L5" s="4">
-        <v>480</v>
+        <v>7</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>41</v>
@@ -1228,10 +1126,10 @@
         <v>45</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>46</v>
@@ -1240,16 +1138,16 @@
         <v>47</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Y5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="Z5" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.72951388889</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>46</v>
@@ -1261,13 +1159,13 @@
         <v>46</v>
       </c>
       <c r="AE5" s="5">
-        <v>45238.46033564815</v>
+        <v>45246.73861111111</v>
       </c>
       <c r="AF5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG5" s="5">
-        <v>45238.46035879629</v>
+        <v>45246.738645833335</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1275,19 +1173,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>38</v>
@@ -1302,10 +1200,10 @@
         <v>40</v>
       </c>
       <c r="K6" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>41</v>
@@ -1326,10 +1224,10 @@
         <v>45</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>46</v>
@@ -1338,34 +1236,31 @@
         <v>47</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.73003472222</v>
       </c>
       <c r="AB6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC6" s="4">
-        <v>0</v>
-      </c>
       <c r="AD6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE6" s="5">
-        <v>45238.460381944446</v>
+        <v>45246.73842592593</v>
       </c>
       <c r="AF6" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG6" s="5">
-        <v>45238.46040509259</v>
+        <v>45246.73844907407</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1373,19 +1268,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>38</v>
@@ -1400,10 +1295,10 @@
         <v>40</v>
       </c>
       <c r="K7" s="4">
-        <v>480</v>
+        <v>8</v>
       </c>
       <c r="L7" s="4">
-        <v>480</v>
+        <v>8</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>41</v>
@@ -1424,10 +1319,10 @@
         <v>45</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>46</v>
@@ -1436,34 +1331,31 @@
         <v>47</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="Z7" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.72951388889</v>
       </c>
       <c r="AB7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC7" s="4">
-        <v>0</v>
-      </c>
       <c r="AD7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE7" s="5">
-        <v>45238.46035879629</v>
+        <v>45246.73856481482</v>
       </c>
       <c r="AF7" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG7" s="5">
-        <v>45238.460381944446</v>
+        <v>45246.73858796296</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1471,19 +1363,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>38</v>
@@ -1498,10 +1390,10 @@
         <v>40</v>
       </c>
       <c r="K8" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4">
-        <v>480</v>
+        <v>5</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>41</v>
@@ -1522,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>46</v>
@@ -1534,31 +1426,34 @@
         <v>47</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="Z8" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.73003472222</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
       <c r="AD8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE8" s="5">
-        <v>45238.460277777776</v>
+        <v>45246.73846064815</v>
       </c>
       <c r="AF8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG8" s="5">
-        <v>45238.46030092593</v>
+        <v>45246.738483796296</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1566,19 +1461,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>38</v>
@@ -1593,10 +1488,10 @@
         <v>40</v>
       </c>
       <c r="K9" s="4">
-        <v>480</v>
+        <v>8</v>
       </c>
       <c r="L9" s="4">
-        <v>480</v>
+        <v>8</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>41</v>
@@ -1617,10 +1512,10 @@
         <v>45</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>46</v>
@@ -1629,31 +1524,34 @@
         <v>47</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="Z9" s="5">
-        <v>45238.45959490741</v>
+        <v>45246.72951388889</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="AC9" s="4">
+        <v>0</v>
+      </c>
       <c r="AD9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE9" s="5">
-        <v>45238.46025462963</v>
+        <v>45246.73858796296</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG9" s="5">
-        <v>45238.460277777776</v>
+        <v>45246.73861111111</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1661,19 +1559,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>38</v>
@@ -1688,10 +1586,10 @@
         <v>40</v>
       </c>
       <c r="K10" s="4">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>41</v>
@@ -1712,10 +1610,10 @@
         <v>45</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>46</v>
@@ -1724,34 +1622,31 @@
         <v>47</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="Z10" s="5">
-        <v>45238.46921296296</v>
+        <v>45246.73013888889</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC10" s="4">
-        <v>0</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE10" s="5">
-        <v>45238.47211805556</v>
+        <v>45246.739004629635</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG10" s="5">
-        <v>45238.4721412037</v>
+        <v>45246.739027777774</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1759,13 +1654,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>36</v>
@@ -1786,10 +1681,10 @@
         <v>40</v>
       </c>
       <c r="K11" s="4">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L11" s="4">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>41</v>
@@ -1825,340 +1720,46 @@
         <v>48</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Z11" s="5">
-        <v>45238.460810185185</v>
+        <v>45246.7295949074</v>
       </c>
       <c r="AB11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC11" s="4">
-        <v>0</v>
-      </c>
       <c r="AD11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AE11" s="5">
-        <v>45238.46098379629</v>
+        <v>45246.7391550926</v>
       </c>
       <c r="AF11" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AG11" s="5">
-        <v>45238.461006944446</v>
+        <v>45246.739178240736</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="4">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4">
-        <v>2</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z12" s="5">
-        <v>45238.470046296294</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE12" s="5">
-        <v>45238.471400462964</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG12" s="5">
-        <v>45238.47142361111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="4">
-        <v>50</v>
-      </c>
-      <c r="L13" s="4">
-        <v>50</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>45238.46229166667</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE13" s="5">
-        <v>45238.46261574074</v>
-      </c>
-      <c r="AF13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG13" s="5">
-        <v>45238.46265046296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="4">
-        <v>245</v>
-      </c>
-      <c r="L14" s="4">
-        <v>245</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z14" s="5">
-        <v>45238.462743055556</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE14" s="5">
-        <v>45238.46332175926</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG14" s="5">
-        <v>45238.4633449074</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="I15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>112</v>
+      <c r="I12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG15"/>
+  <autoFilter ref="A1:AG12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
